--- a/docs/Mapping_casi_uso/cittadinanza/Citt_004.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_004.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="188">
   <si>
     <t>Sezione</t>
   </si>
@@ -476,6 +476,33 @@
     <t>evento.padre.recapito</t>
   </si>
   <si>
+    <t>Dati accertamento</t>
+  </si>
+  <si>
+    <t>Data accertamento</t>
+  </si>
+  <si>
+    <t>evento.enteDichiarante</t>
+  </si>
+  <si>
+    <t>dataTrascrizione</t>
+  </si>
+  <si>
+    <t>Numero accertamento</t>
+  </si>
+  <si>
+    <t>estremiDocumento</t>
+  </si>
+  <si>
+    <t>Atto collegato di Cittadinanza</t>
+  </si>
+  <si>
+    <t>evento.eventoCollegatoCittadinanza</t>
+  </si>
+  <si>
+    <t>opzionale</t>
+  </si>
+  <si>
     <t>Autorità mittente</t>
   </si>
   <si>
@@ -485,13 +512,7 @@
     <t>evento.trascrizioneCittadinanza.atto.enteEstero</t>
   </si>
   <si>
-    <t>dataTrascrizione</t>
-  </si>
-  <si>
     <t>Estremi documento</t>
-  </si>
-  <si>
-    <t>estremiDocumento</t>
   </si>
   <si>
     <t>Nome ente</t>
@@ -613,10 +634,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="19.0625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.4296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="43.9609375" customWidth="true" bestFit="true"/>
@@ -3525,231 +3546,576 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>160</v>
+        <v>101</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>161</v>
+        <v>103</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>18</v>
+        <v>162</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B128" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G128" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="F128" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G128" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>164</v>
+        <v>106</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>18</v>
+        <v>162</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>166</v>
+        <v>108</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>167</v>
+        <v>109</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>18</v>
+        <v>162</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>168</v>
+        <v>110</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>18</v>
+        <v>162</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>18</v>
+        <v>162</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>172</v>
+        <v>114</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>173</v>
+        <v>17</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>18</v>
+        <v>162</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>174</v>
+        <v>115</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>175</v>
+        <v>116</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>18</v>
+        <v>162</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>176</v>
+        <v>117</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>177</v>
+        <v>20</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>18</v>
+        <v>162</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E147" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="F147" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B148" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C136" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D136" s="2" t="s">
+      <c r="C148" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D151" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E136" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F136" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G136" s="2" t="s">
+      <c r="E151" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G151" s="2" t="s">
         <v>18</v>
       </c>
     </row>
